--- a/InputData/elec/SYTaDC/Start Year Transmission and Distribution Costs.xlsx
+++ b/InputData/elec/SYTaDC/Start Year Transmission and Distribution Costs.xlsx
@@ -2765,7 +2765,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{982CC211-5AAA-4860-9DEC-3486292ECCCC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F833857-7F1A-43BF-9670-8356B7F0C30B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2773,5 +2773,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9659FA89-68D4-4AEC-9323-51F365F4BBD9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A9F5549-7252-4E6F-86F1-3D044561190C}"/>
 </file>